--- a/tame_output/ON/bt/strategyON_20240316.xlsx
+++ b/tame_output/ON/bt/strategyON_20240316.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-289.8%</t>
+          <t>-289.6%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-1.281859324840795</v>
+        <v>-1.280020593368816</v>
       </c>
       <c r="E1904" t="n">
-        <v>2.639865303277267</v>
+        <v>2.640600795866059</v>
       </c>
       <c r="F1904" t="n">
-        <v>1.543107447448618</v>
+        <v>1.542970361381044</v>
       </c>
       <c r="G1904" t="n">
-        <v>4.078829925996503</v>
+        <v>4.078747674355959</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240316.xlsx
+++ b/tame_output/ON/bt/strategyON_20240316.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-53.5%</t>
+          <t>-55.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-45.3%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>469.3%</t>
+          <t>468.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-289.6%</t>
+          <t>-308.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-112.2%</t>
+          <t>-119.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-69.7%</t>
+          <t>-76.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-38.1%</t>
+          <t>-42.3%</t>
         </is>
       </c>
     </row>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199884</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078594</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880266</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234391</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.49371243886058</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767394</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792538</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628916</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410712</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240573</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085275</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702413</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83324917230973</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.544283825361691</v>
+        <v>3.544283825361688</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-1.280020593368816</v>
+        <v>-1.473533185292652</v>
       </c>
       <c r="E1904" t="n">
-        <v>2.640600795866059</v>
+        <v>2.563195759096525</v>
       </c>
       <c r="F1904" t="n">
-        <v>1.542970361381044</v>
+        <v>1.47321173951631</v>
       </c>
       <c r="G1904" t="n">
-        <v>4.078747674355959</v>
+        <v>4.036892501237118</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240316.xlsx
+++ b/tame_output/ON/bt/strategyON_20240316.xlsx
@@ -43658,7 +43658,7 @@
         <v>45293</v>
       </c>
       <c r="B1831" t="n">
-        <v>3.346417924612275</v>
+        <v>3.346417924612274</v>
       </c>
       <c r="C1831" t="n">
         <v>3.12760327346781</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.29873059070667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969595</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199884</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910627</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078594</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880266</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234391</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.49371243886058</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767394</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792538</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628916</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410712</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240573</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085275</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.83324917230973</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.839370871858732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.544283825361688</v>
+        <v>3.544283825361691</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>

--- a/tame_output/ON/bt/strategyON_20240316.xlsx
+++ b/tame_output/ON/bt/strategyON_20240316.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>17.0%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>-17.8%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-55.0%</t>
+          <t>-57.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -969,11 +969,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-50.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>468.5%</t>
+          <t>466.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-308.9%</t>
+          <t>-331.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1127,11 +1127,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-119.9%</t>
+          <t>-129.1%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1285,11 +1285,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-210.6%</t>
+          <t>-167.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-99.1%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>83.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>50.2%</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>89.2%</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>37.0%</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-42.3%</t>
+          <t>-152.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1904"/>
+  <dimension ref="A1:G1905"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-6.478328927064983</v>
+        <v>-6.707542035304986</v>
       </c>
       <c r="E1878" t="n">
-        <v>0.5457385407939341</v>
+        <v>0.454053297497933</v>
       </c>
       <c r="F1878" t="n">
-        <v>-0.8633693832348741</v>
+        <v>-1.087244637691088</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.61940490599275</v>
+        <v>2.485079753319022</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199884</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-6.427301080983157</v>
+        <v>-6.656514189223159</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.5706322337111005</v>
+        <v>0.4789469904150998</v>
       </c>
       <c r="F1879" t="n">
-        <v>-0.7881600449277731</v>
+        <v>-1.012035299383987</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.669013063461447</v>
+        <v>2.534687910787719</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-6.353831249315709</v>
+        <v>-6.583044357555711</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.6153918678715011</v>
+        <v>0.5237066245755</v>
       </c>
       <c r="F1880" t="n">
-        <v>-0.7146902132603248</v>
+        <v>-0.9385654677165385</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.728466663955337</v>
+        <v>2.594141511281609</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078594</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-6.273458893851779</v>
+        <v>-6.502672002091781</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.66209603080459</v>
+        <v>0.5704107875085889</v>
       </c>
       <c r="F1881" t="n">
-        <v>-0.6343178577963952</v>
+        <v>-0.8581931122526089</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.791245297981212</v>
+        <v>2.656920145307484</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880266</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-6.240527024038928</v>
+        <v>-6.469740132278931</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.668049613828134</v>
+        <v>0.5763643705321333</v>
       </c>
       <c r="F1882" t="n">
-        <v>-0.6343178577963952</v>
+        <v>-0.8581931122526089</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.784026133079616</v>
+        <v>2.649700980405888</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234391</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-6.260691665588475</v>
+        <v>-6.489904773828478</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.653311566434339</v>
+        <v>0.5616263231383383</v>
       </c>
       <c r="F1883" t="n">
-        <v>-0.6544824993459425</v>
+        <v>-0.8783577538021562</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.765255157375911</v>
+        <v>2.630930004702183</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.49371243886058</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-6.202024735566942</v>
+        <v>-6.431237843806945</v>
       </c>
       <c r="E1884" t="n">
-        <v>0.6778941282815087</v>
+        <v>0.5862088849855076</v>
       </c>
       <c r="F1884" t="n">
-        <v>-0.5695230309158048</v>
+        <v>-0.7933982853720185</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.81734662827255</v>
+        <v>2.683021475598822</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767394</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-6.138955503260602</v>
+        <v>-6.368168611500606</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.7058155498331593</v>
+        <v>0.6141303065371582</v>
       </c>
       <c r="F1885" t="n">
-        <v>-0.5980365935980393</v>
+        <v>-0.821911848054253</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.802932219292324</v>
+        <v>2.668607066618596</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792538</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-6.08693998929179</v>
+        <v>-6.316153097531793</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.7306120911070852</v>
+        <v>0.6389268478110837</v>
       </c>
       <c r="F1886" t="n">
-        <v>-0.5980365935980393</v>
+        <v>-0.821911848054253</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.806922554978725</v>
+        <v>2.672597402304997</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628916</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-5.911370320370886</v>
+        <v>-6.140583428610889</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.7993647317767052</v>
+        <v>0.7076794884807036</v>
       </c>
       <c r="F1887" t="n">
-        <v>-0.5980365935980393</v>
+        <v>-0.821911848054253</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.805447328079984</v>
+        <v>2.671122175406255</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410712</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-5.714100914642888</v>
+        <v>-5.943314022882891</v>
       </c>
       <c r="E1888" t="n">
-        <v>0.8933259042327766</v>
+        <v>0.8016406609367754</v>
       </c>
       <c r="F1888" t="n">
-        <v>-0.4007671878700412</v>
+        <v>-0.6246424423262549</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.938862381681655</v>
+        <v>2.804537229007926</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240573</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-5.514948807405789</v>
+        <v>-5.744161915645792</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.9599356134809334</v>
+        <v>0.8682503701849318</v>
       </c>
       <c r="F1889" t="n">
-        <v>-0.2354446619202278</v>
+        <v>-0.4593199163764415</v>
       </c>
       <c r="G1889" t="n">
-        <v>3.025004763604859</v>
+        <v>2.890679610931131</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085275</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-5.289103654686378</v>
+        <v>-5.518316762926381</v>
       </c>
       <c r="E1890" t="n">
-        <v>1.059852747604906</v>
+        <v>0.9681675043089051</v>
       </c>
       <c r="F1890" t="n">
-        <v>-0.1935179863330642</v>
+        <v>-0.4173932407892779</v>
       </c>
       <c r="G1890" t="n">
-        <v>3.059739841993367</v>
+        <v>2.925414689319638</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-5.002828842363684</v>
+        <v>-5.232041950603687</v>
       </c>
       <c r="E1891" t="n">
-        <v>1.175501817090043</v>
+        <v>1.083816573794041</v>
       </c>
       <c r="F1891" t="n">
-        <v>-0.1935179863330642</v>
+        <v>-0.4173932407892779</v>
       </c>
       <c r="G1891" t="n">
-        <v>3.060878986549425</v>
+        <v>2.926553833875697</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-4.77603301529035</v>
+        <v>-5.005246123530354</v>
       </c>
       <c r="E1892" t="n">
-        <v>1.268853922081484</v>
+        <v>1.177168678785482</v>
       </c>
       <c r="F1892" t="n">
-        <v>-0.1254040417115196</v>
+        <v>-0.3492792961677333</v>
       </c>
       <c r="G1892" t="n">
-        <v>3.104381127484459</v>
+        <v>2.970055974810732</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-4.492124284361601</v>
+        <v>-4.721337392601605</v>
       </c>
       <c r="E1893" t="n">
-        <v>1.38815111869162</v>
+        <v>1.296465875395619</v>
       </c>
       <c r="F1893" t="n">
-        <v>-0.1254040417115196</v>
+        <v>-0.3492792961677333</v>
       </c>
       <c r="G1893" t="n">
-        <v>3.110114831723096</v>
+        <v>2.975789679049368</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-4.245137034168649</v>
+        <v>-4.474350142408652</v>
       </c>
       <c r="E1894" t="n">
-        <v>1.477208756374936</v>
+        <v>1.385523513078934</v>
       </c>
       <c r="F1894" t="n">
-        <v>0.1215832084814324</v>
+        <v>-0.1022920459747813</v>
       </c>
       <c r="G1894" t="n">
-        <v>3.248569919445002</v>
+        <v>3.114244766771274</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702413</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-3.98130016696458</v>
+        <v>-4.210513275204583</v>
       </c>
       <c r="E1895" t="n">
-        <v>1.572860021943656</v>
+        <v>1.481174778647654</v>
       </c>
       <c r="F1895" t="n">
-        <v>0.1215832084814324</v>
+        <v>-0.1022920459747813</v>
       </c>
       <c r="G1895" t="n">
-        <v>3.238686438132095</v>
+        <v>3.104361285458366</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-3.714058366096183</v>
+        <v>-3.943271474336187</v>
       </c>
       <c r="E1896" t="n">
-        <v>1.677922181791641</v>
+        <v>1.586236938495639</v>
       </c>
       <c r="F1896" t="n">
-        <v>0.1215832084814324</v>
+        <v>-0.1022920459747813</v>
       </c>
       <c r="G1896" t="n">
-        <v>3.236851877632721</v>
+        <v>3.102526724958993</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-3.438249202695699</v>
+        <v>-3.667462310935703</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.787945532178373</v>
+        <v>1.696260288882372</v>
       </c>
       <c r="F1897" t="n">
-        <v>0.2106025167601659</v>
+        <v>-0.01327273769604775</v>
       </c>
       <c r="G1897" t="n">
-        <v>3.2899631476265</v>
+        <v>3.155637994952772</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-3.16918161492872</v>
+        <v>-3.398394723168723</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.896241073430659</v>
+        <v>1.804555830134657</v>
       </c>
       <c r="F1898" t="n">
-        <v>0.4796701045271453</v>
+        <v>0.2557948500709316</v>
       </c>
       <c r="G1898" t="n">
-        <v>3.452072206432181</v>
+        <v>3.317747053758453</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-2.905121676605924</v>
+        <v>-3.134334784845927</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.988604732598025</v>
+        <v>1.896919489302024</v>
       </c>
       <c r="F1899" t="n">
-        <v>0.7437300428499415</v>
+        <v>0.5198547883937278</v>
       </c>
       <c r="G1899" t="n">
-        <v>3.597247853264107</v>
+        <v>3.462922700590379</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83324917230973</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-2.198042053101086</v>
+        <v>-2.427255161341089</v>
       </c>
       <c r="E1900" t="n">
-        <v>2.268649548339659</v>
+        <v>2.176964305043658</v>
       </c>
       <c r="F1900" t="n">
-        <v>0.7437300428499415</v>
+        <v>0.5198547883937278</v>
       </c>
       <c r="G1900" t="n">
-        <v>3.594460819603806</v>
+        <v>3.460135666930078</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-1.948401023115134</v>
+        <v>-2.177614131355138</v>
       </c>
       <c r="E1901" t="n">
-        <v>2.368849584221882</v>
+        <v>2.27716434092588</v>
       </c>
       <c r="F1901" t="n">
-        <v>0.9933710728358931</v>
+        <v>0.7694958183796795</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.744589061483218</v>
+        <v>3.61026390880949</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-1.693859123774059</v>
+        <v>-1.923072232014062</v>
       </c>
       <c r="E1902" t="n">
-        <v>2.470033165179069</v>
+        <v>2.378347921883067</v>
       </c>
       <c r="F1902" t="n">
-        <v>1.247912972176969</v>
+        <v>1.024037717720755</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.896681022308621</v>
+        <v>3.762355869634892</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-1.46037790154446</v>
+        <v>-1.689591009784464</v>
       </c>
       <c r="E1903" t="n">
-        <v>2.571350082908761</v>
+        <v>2.479664839612759</v>
       </c>
       <c r="F1903" t="n">
-        <v>1.481394194406567</v>
+        <v>1.257518939950354</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.044694184484232</v>
+        <v>3.910369031810504</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,45 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.544283825361691</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-1.473533185292652</v>
+        <v>-1.702746293532655</v>
       </c>
       <c r="E1904" t="n">
-        <v>2.563195759096525</v>
+        <v>2.471510515800523</v>
       </c>
       <c r="F1904" t="n">
-        <v>1.47321173951631</v>
+        <v>1.249336485060096</v>
       </c>
       <c r="G1904" t="n">
-        <v>4.036892501237118</v>
+        <v>3.90256734856339</v>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" s="2" t="n">
+        <v>45367</v>
+      </c>
+      <c r="B1905" t="n">
+        <v>3.451154711034953</v>
+      </c>
+      <c r="C1905" t="n">
+        <v>2.938176916709865</v>
+      </c>
+      <c r="D1905" t="n">
+        <v>-1.702746293532655</v>
+      </c>
+      <c r="E1905" t="n">
+        <v>2.471510515800523</v>
+      </c>
+      <c r="F1905" t="n">
+        <v>1.249336485060096</v>
+      </c>
+      <c r="G1905" t="n">
+        <v>2.931240713696233</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240316.xlsx
+++ b/tame_output/ON/bt/strategyON_20240316.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>15.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-57.2%</t>
+          <t>-58.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>110.2%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -969,11 +969,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-325.1%</t>
+          <t>-332.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1127,11 +1127,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-126.4%</t>
+          <t>-129.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1285,11 +1285,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-213.9%</t>
+          <t>-208.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-105.6%</t>
+          <t>-110.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-157.6%</t>
+          <t>-63.0%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.301413393085798</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705545</v>
+        <v>3.311607601705546</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045692</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831153</v>
+        <v>3.320996253831154</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347058</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.28737757613002</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207815</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310984</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006536</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309427</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970908</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330526</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097825</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341318</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776681</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-6.782204844798464</v>
+        <v>-7.044763735695254</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.428670728184978</v>
+        <v>0.3236471718262619</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.14306380874308</v>
+        <v>-1.375455278536962</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.456070805172263</v>
+        <v>2.316635923295934</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-6.708735013131016</v>
+        <v>-6.971293904027806</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.4734303623453782</v>
+        <v>0.3684068059866625</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.069593977075632</v>
+        <v>-1.301985446869514</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.515524405666153</v>
+        <v>2.376089523789824</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-6.628362657667086</v>
+        <v>-6.890921548563876</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.520134525278467</v>
+        <v>0.415110968919751</v>
       </c>
       <c r="F1881" t="n">
-        <v>-0.9892216216117021</v>
+        <v>-1.221613091405584</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.578303039692028</v>
+        <v>2.438868157815699</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-6.595430787854236</v>
+        <v>-6.857989678751025</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.526088108302011</v>
+        <v>0.4210645519432954</v>
       </c>
       <c r="F1882" t="n">
-        <v>-0.9892216216117021</v>
+        <v>-1.221613091405584</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.571083874790432</v>
+        <v>2.431648992914103</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-6.615595429403783</v>
+        <v>-6.878154320300572</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.511350060908216</v>
+        <v>0.4063265045495004</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.009386263161249</v>
+        <v>-1.241777732955131</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.552312899086727</v>
+        <v>2.412878017210398</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-6.556928499382249</v>
+        <v>-6.819487390279039</v>
       </c>
       <c r="E1884" t="n">
-        <v>0.5359326227553858</v>
+        <v>0.4309090663966701</v>
       </c>
       <c r="F1884" t="n">
-        <v>-0.9244267947311117</v>
+        <v>-1.156818264524994</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.604404369983366</v>
+        <v>2.464969488107037</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-6.49385926707591</v>
+        <v>-6.7564181579727</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.5638540443070359</v>
+        <v>0.4588304879483203</v>
       </c>
       <c r="F1885" t="n">
-        <v>-0.9529403574133462</v>
+        <v>-1.185331827207228</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.58998996100314</v>
+        <v>2.450555079126811</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-6.441843753107098</v>
+        <v>-6.704402644003888</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.5886505855809618</v>
+        <v>0.4836270292222462</v>
       </c>
       <c r="F1886" t="n">
-        <v>-0.9529403574133462</v>
+        <v>-1.185331827207228</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.593980296689541</v>
+        <v>2.454545414813212</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-6.266274084186194</v>
+        <v>-6.528832975082984</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.6574032262505818</v>
+        <v>0.5523796698918657</v>
       </c>
       <c r="F1887" t="n">
-        <v>-0.9529403574133462</v>
+        <v>-1.185331827207228</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.592505069790799</v>
+        <v>2.45307018791447</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-6.069004678458196</v>
+        <v>-6.331563569354985</v>
       </c>
       <c r="E1888" t="n">
-        <v>0.7513643987066532</v>
+        <v>0.6463408423479375</v>
       </c>
       <c r="F1888" t="n">
-        <v>-0.755670951685348</v>
+        <v>-0.9880624214792301</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.72592012339247</v>
+        <v>2.586485241516141</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-5.869852571221097</v>
+        <v>-6.132411462117886</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.81797410795481</v>
+        <v>0.7129505515960939</v>
       </c>
       <c r="F1889" t="n">
-        <v>-0.5903484257355347</v>
+        <v>-0.8227398955294167</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.812062505315676</v>
+        <v>2.672627623439346</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-5.644007418501686</v>
+        <v>-5.906566309398475</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.9178912420787828</v>
+        <v>0.8128676857200672</v>
       </c>
       <c r="F1890" t="n">
-        <v>-0.548421750148371</v>
+        <v>-0.7808132199422531</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.846797583704182</v>
+        <v>2.707362701827853</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-5.357732606178992</v>
+        <v>-5.620291497075781</v>
       </c>
       <c r="E1891" t="n">
-        <v>1.033540311563919</v>
+        <v>0.9285167552052038</v>
       </c>
       <c r="F1891" t="n">
-        <v>-0.548421750148371</v>
+        <v>-0.7808132199422531</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.847936728260241</v>
+        <v>2.708501846383912</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-5.130936779105658</v>
+        <v>-5.393495670002448</v>
       </c>
       <c r="E1892" t="n">
-        <v>1.126892416555361</v>
+        <v>1.021868860196645</v>
       </c>
       <c r="F1892" t="n">
-        <v>-0.4803078055268265</v>
+        <v>-0.7126992753207085</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.891438869195276</v>
+        <v>2.752003987318946</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081565</v>
+        <v>3.76894809908157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-4.847028048176909</v>
+        <v>-5.109586939073699</v>
       </c>
       <c r="E1893" t="n">
-        <v>1.246189613165497</v>
+        <v>1.141166056806781</v>
       </c>
       <c r="F1893" t="n">
-        <v>-0.4803078055268265</v>
+        <v>-0.7126992753207085</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.897172573433912</v>
+        <v>2.757737691557583</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-4.600040797983957</v>
+        <v>-4.862599688880747</v>
       </c>
       <c r="E1894" t="n">
-        <v>1.335247250848812</v>
+        <v>1.230223694490097</v>
       </c>
       <c r="F1894" t="n">
-        <v>-0.2333205553338744</v>
+        <v>-0.4657120251277564</v>
       </c>
       <c r="G1894" t="n">
-        <v>3.035627661155818</v>
+        <v>2.896192779279489</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-4.336203930779888</v>
+        <v>-4.598762821676678</v>
       </c>
       <c r="E1895" t="n">
-        <v>1.430898516417532</v>
+        <v>1.325874960058817</v>
       </c>
       <c r="F1895" t="n">
-        <v>-0.2333205553338744</v>
+        <v>-0.4657120251277564</v>
       </c>
       <c r="G1895" t="n">
-        <v>3.02574417984291</v>
+        <v>2.886309297966581</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906226</v>
+        <v>3.766313503906231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-4.068962129911491</v>
+        <v>-4.331521020808281</v>
       </c>
       <c r="E1896" t="n">
-        <v>1.535960676265517</v>
+        <v>1.430937119906802</v>
       </c>
       <c r="F1896" t="n">
-        <v>-0.2333205553338744</v>
+        <v>-0.4657120251277564</v>
       </c>
       <c r="G1896" t="n">
-        <v>3.023909619343537</v>
+        <v>2.884474737467208</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781951</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-3.793152966511007</v>
+        <v>-4.055711857407797</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.64598402665225</v>
+        <v>1.540960470293534</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.1443012470551409</v>
+        <v>-0.3766927168490229</v>
       </c>
       <c r="G1897" t="n">
-        <v>3.077020889337316</v>
+        <v>2.937586007460987</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567247</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-3.524085378744028</v>
+        <v>-3.786644269640818</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.754279567904536</v>
+        <v>1.64925601154582</v>
       </c>
       <c r="F1898" t="n">
-        <v>0.1247663407118385</v>
+        <v>-0.1076251290820436</v>
       </c>
       <c r="G1898" t="n">
-        <v>3.239129948142997</v>
+        <v>3.099695066266668</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487776</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-3.260025440421232</v>
+        <v>-3.522584331318021</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.846643227071902</v>
+        <v>1.741619670713186</v>
       </c>
       <c r="F1899" t="n">
-        <v>0.3888262790346346</v>
+        <v>0.1564348092407526</v>
       </c>
       <c r="G1899" t="n">
-        <v>3.384305594974923</v>
+        <v>3.244870713098594</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.83324917230973</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-2.552945816916394</v>
+        <v>-2.815504707813183</v>
       </c>
       <c r="E1900" t="n">
-        <v>2.126688042813536</v>
+        <v>2.02166448645482</v>
       </c>
       <c r="F1900" t="n">
-        <v>0.3888262790346346</v>
+        <v>0.1564348092407526</v>
       </c>
       <c r="G1900" t="n">
-        <v>3.381518561314622</v>
+        <v>3.242083679438293</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.839370871858732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-2.303304786930442</v>
+        <v>-2.565863677827232</v>
       </c>
       <c r="E1901" t="n">
-        <v>2.226888078695758</v>
+        <v>2.121864522337042</v>
       </c>
       <c r="F1901" t="n">
-        <v>0.6384673090205863</v>
+        <v>0.4060758392267043</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.531646803194034</v>
+        <v>3.392211921317705</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-2.048762887589367</v>
+        <v>-2.311321778486156</v>
       </c>
       <c r="E1902" t="n">
-        <v>2.328071659652945</v>
+        <v>2.22304810329423</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.8930092083616619</v>
+        <v>0.6606177385677798</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.683738764019437</v>
+        <v>3.544303882143107</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-1.815281665359768</v>
+        <v>-2.077840556256558</v>
       </c>
       <c r="E1903" t="n">
-        <v>2.429388577382637</v>
+        <v>2.324365021023922</v>
       </c>
       <c r="F1903" t="n">
-        <v>1.12649043059126</v>
+        <v>0.8940989607973784</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.831751926195048</v>
+        <v>3.692317044318719</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-1.635573135215896</v>
+        <v>-1.898132026112685</v>
       </c>
       <c r="E1904" t="n">
-        <v>2.498379779127227</v>
+        <v>2.393356222768511</v>
       </c>
       <c r="F1904" t="n">
-        <v>1.183661934753957</v>
+        <v>0.9512704649600745</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.863162618379707</v>
+        <v>3.723727736503378</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.420783643491235</v>
+        <v>3.439654578159369</v>
       </c>
       <c r="C1905" t="n">
-        <v>2.891024863964763</v>
+        <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-1.635573135215896</v>
+        <v>-1.712640208363002</v>
       </c>
       <c r="E1905" t="n">
-        <v>2.498379779127227</v>
+        <v>2.462920436615411</v>
       </c>
       <c r="F1905" t="n">
-        <v>1.183661934753957</v>
+        <v>1.136762282709758</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.884088660951131</v>
+        <v>3.830390313900215</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240316.xlsx
+++ b/tame_output/ON/bt/strategyON_20240316.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-58.2%</t>
+          <t>-54.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-428.0%</t>
+          <t>-392.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-46.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>476.8%</t>
+          <t>467.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-332.8%</t>
+          <t>-299.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-171.6%</t>
+          <t>-157.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-129.9%</t>
+          <t>-116.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.7%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-232.4%</t>
+          <t>-196.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-208.6%</t>
+          <t>-173.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-110.3%</t>
+          <t>-75.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>88.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-139.9%</t>
+          <t>-118.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-63.0%</t>
+          <t>-42.1%</t>
         </is>
       </c>
     </row>
@@ -43687,16 +43687,16 @@
         <v>3.130069279090508</v>
       </c>
       <c r="D1832" t="n">
-        <v>0.8875070250904159</v>
+        <v>1.242410788905723</v>
       </c>
       <c r="E1832" t="n">
-        <v>3.484715664812927</v>
+        <v>3.62667717033905</v>
       </c>
       <c r="F1832" t="n">
-        <v>1.861371945398691</v>
+        <v>2.216275709213999</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.246892446329723</v>
+        <v>4.459834704618908</v>
       </c>
     </row>
     <row r="1833">
@@ -43704,22 +43704,22 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705546</v>
+        <v>3.311607601705545</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
       </c>
       <c r="D1833" t="n">
-        <v>0.8396686628442172</v>
+        <v>1.194572426659524</v>
       </c>
       <c r="E1833" t="n">
-        <v>3.46245237381616</v>
+        <v>3.604413879342283</v>
       </c>
       <c r="F1833" t="n">
-        <v>1.861371945398691</v>
+        <v>2.216275709213999</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.243764500231435</v>
+        <v>4.45670675852062</v>
       </c>
     </row>
     <row r="1834">
@@ -43727,22 +43727,22 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045692</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.7683205556046431</v>
+        <v>1.12322431941995</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.44688974020372</v>
+        <v>3.588851245729843</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.790023838159117</v>
+        <v>2.144927601974425</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.213932245171081</v>
+        <v>4.426874503460265</v>
       </c>
     </row>
     <row r="1835">
@@ -43750,22 +43750,22 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831153</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.7677687557628309</v>
+        <v>1.122672519578138</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.44492685612934</v>
+        <v>3.586888361655462</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.790865601644424</v>
+        <v>2.145769365459731</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.212695139124609</v>
+        <v>4.425637397413793</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.6620818678205311</v>
+        <v>1.016985631635838</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.382477373579867</v>
+        <v>3.52443887910599</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.77630452794174</v>
+        <v>2.131208291757047</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.183783767530446</v>
+        <v>4.39672602581963</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.6679312489357755</v>
+        <v>1.022835012751082</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.385306264751839</v>
+        <v>3.527267770277962</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.77630452794174</v>
+        <v>2.131208291757047</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.184272906256321</v>
+        <v>4.397215164545504</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.619708982088692</v>
+        <v>0.9746127459039988</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.370097340634672</v>
+        <v>3.512058846160795</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.728082261094657</v>
+        <v>2.082986024909964</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.159419528769737</v>
+        <v>4.372361787058921</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.6275442439255763</v>
+        <v>0.9824480077408831</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.408172529866968</v>
+        <v>3.55013403539309</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.728082261094657</v>
+        <v>2.082986024909964</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.194360613267278</v>
+        <v>4.407302871556463</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998562</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.6325818346531629</v>
+        <v>0.9874855984684696</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.40876500634334</v>
+        <v>3.550726511869463</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.783726717360974</v>
+        <v>2.138630481176281</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.226324727212407</v>
+        <v>4.439266985501591</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.5761122034768661</v>
+        <v>0.9310159672921728</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.364923535496559</v>
+        <v>3.506885041022681</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.727257086184677</v>
+        <v>2.082160849999984</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.171189330130366</v>
+        <v>4.38413158841955</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.510344813427454</v>
+        <v>0.8652485772427607</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.339634188607264</v>
+        <v>3.481595694133387</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.727257086184677</v>
+        <v>2.082160849999984</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.172206939260836</v>
+        <v>4.38514919755002</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.4968093296507443</v>
+        <v>0.8517130934660511</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.324848027084336</v>
+        <v>3.466809532610458</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.727257086184677</v>
+        <v>2.082160849999984</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.162834971248592</v>
+        <v>4.375777229537776</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.4150374292229926</v>
+        <v>0.7699411930382993</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.282221992868473</v>
+        <v>3.424183498394596</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.754292659590813</v>
+        <v>2.109196423406121</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.169139041247512</v>
+        <v>4.382081299536696</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.347828321351115</v>
+        <v>0.7027320851664216</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.260103666553424</v>
+        <v>3.402065172079547</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.754292659590813</v>
+        <v>2.109196423406121</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.173904358081214</v>
+        <v>4.386846616370399</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.3518197741463052</v>
+        <v>0.7067235379616118</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.259525043790741</v>
+        <v>3.401486549316864</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.758284112386004</v>
+        <v>2.113187876201311</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.174124025877568</v>
+        <v>4.387066284166753</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>0.2001227271023701</v>
+        <v>0.5550264909176768</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.19677311647823</v>
+        <v>3.338734622004353</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.606587065342069</v>
+        <v>1.961490829157376</v>
       </c>
       <c r="G1847" t="n">
-        <v>4.081032689156271</v>
+        <v>4.293974947445455</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.02149920645574738</v>
+        <v>0.3334045573595593</v>
       </c>
       <c r="E1848" t="n">
-        <v>3.107990559653905</v>
+        <v>3.249952065180028</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.5690609316547</v>
+        <v>1.923964695470007</v>
       </c>
       <c r="G1848" t="n">
-        <v>4.058383225542771</v>
+        <v>4.271325483831956</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.2295032648088246</v>
+        <v>0.125400499006482</v>
       </c>
       <c r="E1849" t="n">
-        <v>3.029681080866599</v>
+        <v>3.171642586392722</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.5690609316547</v>
+        <v>1.923964695470007</v>
       </c>
       <c r="G1849" t="n">
-        <v>4.063275370096696</v>
+        <v>4.276217628385881</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.4999032275177099</v>
+        <v>-0.1449994637024033</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.916602552121033</v>
+        <v>3.058564057647156</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.298660968945814</v>
+        <v>1.653564732761122</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.896116848809354</v>
+        <v>4.109059107098537</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-0.5065381500146401</v>
+        <v>-0.1516343861993334</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.90703288242871</v>
+        <v>3.048994387954833</v>
       </c>
       <c r="F1851" t="n">
-        <v>1.292026046448884</v>
+        <v>1.646929810264191</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.885220194617644</v>
+        <v>4.098162452906829</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-0.8345553717421192</v>
+        <v>-0.4796516079268126</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.796164283476487</v>
+        <v>2.938125789002609</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.964008824721405</v>
+        <v>1.318912588536712</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.708748151319925</v>
+        <v>3.921690409609109</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-0.8312186252331476</v>
+        <v>-0.476314861417841</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.805597732488644</v>
+        <v>2.947559238014767</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.9667008571404364</v>
+        <v>1.321604620955744</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.718462121179912</v>
+        <v>3.931404379469097</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.197929676899693</v>
+        <v>-0.8430259130843866</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.660019703865758</v>
+        <v>2.801981209391881</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.5999898054738908</v>
+        <v>0.9548935692891981</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.499541882223717</v>
+        <v>3.712484140512902</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-1.198360375948289</v>
+        <v>-0.8434566121329821</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.658389963059183</v>
+        <v>2.800351468585306</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.5999898054738908</v>
+        <v>0.9548935692891981</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.498084421036581</v>
+        <v>3.711026679325765</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347058</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-1.542043149174951</v>
+        <v>-1.187139385359645</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.522685977223134</v>
+        <v>2.664647482749257</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.4920837534466727</v>
+        <v>0.8469875172619798</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.435109913274866</v>
+        <v>3.64805217156405</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.28737757613002</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-1.899693499413299</v>
+        <v>-1.544789735597993</v>
       </c>
       <c r="E1857" t="n">
-        <v>2.375731895784053</v>
+        <v>2.517693401310175</v>
       </c>
       <c r="F1857" t="n">
-        <v>0.1344334032083245</v>
+        <v>0.4893371670236317</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.216625761788115</v>
+        <v>3.429568020077299</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-1.906354439635447</v>
+        <v>-1.551450675820141</v>
       </c>
       <c r="E1858" t="n">
-        <v>2.374840446395453</v>
+        <v>2.516801951921576</v>
       </c>
       <c r="F1858" t="n">
-        <v>0.1344334032083245</v>
+        <v>0.4893371670236317</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.218398688488374</v>
+        <v>3.431340946777559</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207815</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-2.338160232785235</v>
+        <v>-1.983256468969929</v>
       </c>
       <c r="E1859" t="n">
-        <v>2.188451016602943</v>
+        <v>2.330412522129065</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.001984093232942463</v>
+        <v>0.3529196705823647</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.122881078091019</v>
+        <v>3.335823336380203</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310984</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-2.664592761652978</v>
+        <v>-2.309688997837672</v>
       </c>
       <c r="E1860" t="n">
-        <v>2.046162780057936</v>
+        <v>2.188124285584058</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.08445234374009064</v>
+        <v>0.2704514200752166</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.06168490278882</v>
+        <v>3.274627161078005</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006536</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-2.666156912763281</v>
+        <v>-2.311253148947976</v>
       </c>
       <c r="E1861" t="n">
-        <v>2.04411771126978</v>
+        <v>2.186079216795902</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.08445234374009064</v>
+        <v>0.2704514200752166</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.060265494444785</v>
+        <v>3.27320775273397</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309427</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-3.029783157663594</v>
+        <v>-2.674879393848288</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.905154773543896</v>
+        <v>2.047116279070019</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.1826739806072165</v>
+        <v>0.1722297832080907</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.007820072558752</v>
+        <v>3.220762330847936</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970908</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-3.027356093134876</v>
+        <v>-2.67245232931957</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.905380114361215</v>
+        <v>2.047341619887337</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.1830067624143681</v>
+        <v>0.1718970014009391</v>
       </c>
       <c r="G1863" t="n">
-        <v>3.006874918480292</v>
+        <v>3.219817176769476</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-3.435944870315554</v>
+        <v>-3.081041106500249</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.740706147503702</v>
+        <v>1.882667653029825</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.5915955395950465</v>
+        <v>-0.2366917757797393</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.760483196186644</v>
+        <v>2.973425454475828</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191741</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-3.848927354456648</v>
+        <v>-3.494023590641342</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.570698586318726</v>
+        <v>1.712660091844848</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.5915955395950465</v>
+        <v>-0.2366917757797393</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.755668628658105</v>
+        <v>2.968610886947289</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108643</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-4.265319228743646</v>
+        <v>-3.910415464928339</v>
       </c>
       <c r="E1866" t="n">
-        <v>1.402135887212804</v>
+        <v>1.544097392738927</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.5915955395950465</v>
+        <v>-0.2366917757797393</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.753662679266982</v>
+        <v>2.966604937556166</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097825</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-4.641996239273491</v>
+        <v>-4.287092475458183</v>
       </c>
       <c r="E1867" t="n">
-        <v>1.261723773669545</v>
+        <v>1.403685279195668</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.5915955395950465</v>
+        <v>-0.2366917757797393</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.763921369935661</v>
+        <v>2.976863628224845</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094121</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-4.655711103598602</v>
+        <v>-4.300807339783295</v>
       </c>
       <c r="E1868" t="n">
-        <v>1.252337393085196</v>
+        <v>1.394298898611319</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.5915955395950465</v>
+        <v>-0.2366917757797393</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.760020935081356</v>
+        <v>2.97296319337054</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-4.968535902843581</v>
+        <v>-4.613632139028274</v>
       </c>
       <c r="E1869" t="n">
-        <v>1.125612393442205</v>
+        <v>1.267573898968328</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.5915955395950465</v>
+        <v>-0.2366917757797393</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.758425855136357</v>
+        <v>2.971368113425541</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-4.973348941308918</v>
+        <v>-4.618445177493611</v>
       </c>
       <c r="E1870" t="n">
-        <v>1.127466153985278</v>
+        <v>1.269427659511401</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.5931421742978323</v>
+        <v>-0.2382384104825251</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.761276850243894</v>
+        <v>2.974219108533078</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-5.406698049419155</v>
+        <v>-5.051794285603847</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.9501002062067809</v>
+        <v>1.092061711732903</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.5931421742978323</v>
+        <v>-0.2382384104825251</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.757250545709491</v>
+        <v>2.970192803998675</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-5.789699438161786</v>
+        <v>-5.434795674346478</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.7967975493881441</v>
+        <v>0.938759054914267</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.5931421742978323</v>
+        <v>-0.2382384104825251</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.757148444387907</v>
+        <v>2.970090702677091</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-6.164684764333063</v>
+        <v>-5.809781000517756</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.6493749348910636</v>
+        <v>0.7913364404171865</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.9681275004691098</v>
+        <v>-0.6132237366538026</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.53472876465657</v>
+        <v>2.747671022945755</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-6.524215086837065</v>
+        <v>-6.169311323021757</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.5109131091875128</v>
+        <v>0.6528746147136357</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.9681275004691098</v>
+        <v>-0.6132237366538026</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.540079067954621</v>
+        <v>2.753021326243805</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341318</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-6.850615115502078</v>
+        <v>-6.49571135168677</v>
       </c>
       <c r="E1875" t="n">
-        <v>0.3882691176786852</v>
+        <v>0.5302306232048082</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.294527529134123</v>
+        <v>-0.9396237653188155</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.35215507071279</v>
+        <v>2.565097329001975</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776681</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-6.844138968708518</v>
+        <v>-6.489235204893211</v>
       </c>
       <c r="E1876" t="n">
-        <v>0.3939013270178777</v>
+        <v>0.5358628325440007</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.288051382340563</v>
+        <v>-0.933147618525256</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.359082509410695</v>
+        <v>2.572024767699879</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407496</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-6.840448043752106</v>
+        <v>-6.485544279936799</v>
       </c>
       <c r="E1877" t="n">
-        <v>0.3953776970004426</v>
+        <v>0.5373392025265655</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.288051382340563</v>
+        <v>-0.933147618525256</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.359082509410695</v>
+        <v>2.572024767699879</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-6.833232690880291</v>
+        <v>-6.478328927064983</v>
       </c>
       <c r="E1878" t="n">
-        <v>0.4037770352678112</v>
+        <v>0.5457385407939341</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.218273147050181</v>
+        <v>-0.8633693832348741</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.406462647703566</v>
+        <v>2.61940490599275</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-7.044763735695254</v>
+        <v>-6.71398639228809</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.3236471718262619</v>
+        <v>0.4559581091891274</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.375455278536962</v>
+        <v>-1.033244218676801</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.316635923295934</v>
+        <v>2.52196255921203</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-6.971293904027806</v>
+        <v>-6.640516560620642</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.3684068059866625</v>
+        <v>0.5007177433495276</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.301985446869514</v>
+        <v>-0.9597743870093529</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.376089523789824</v>
+        <v>2.58141615970592</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-6.890921548563876</v>
+        <v>-6.560144205156712</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.415110968919751</v>
+        <v>0.5474219062826164</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.221613091405584</v>
+        <v>-0.8794020315454233</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.438868157815699</v>
+        <v>2.644194793731795</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-6.857989678751025</v>
+        <v>-6.527212335343862</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.4210645519432954</v>
+        <v>0.5533754893061609</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.221613091405584</v>
+        <v>-0.8794020315454233</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.431648992914103</v>
+        <v>2.636975628830199</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-6.878154320300572</v>
+        <v>-6.547376976893409</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.4063265045495004</v>
+        <v>0.5386374419123658</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.241777732955131</v>
+        <v>-0.8995666730949706</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.412878017210398</v>
+        <v>2.618204653126495</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-6.819487390279039</v>
+        <v>-6.488710046871875</v>
       </c>
       <c r="E1884" t="n">
-        <v>0.4309090663966701</v>
+        <v>0.5632200037595352</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.156818264524994</v>
+        <v>-0.8146072046648329</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.464969488107037</v>
+        <v>2.670296124023134</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-6.7564181579727</v>
+        <v>-6.425640814565536</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.4588304879483203</v>
+        <v>0.5911414253111857</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.185331827207228</v>
+        <v>-0.8431207673470674</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.450555079126811</v>
+        <v>2.655881715042907</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-6.704402644003888</v>
+        <v>-6.373625300596724</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.4836270292222462</v>
+        <v>0.6159379665851112</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.185331827207228</v>
+        <v>-0.8431207673470674</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.454545414813212</v>
+        <v>2.659872050729308</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-6.528832975082984</v>
+        <v>-6.19805563167582</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.5523796698918657</v>
+        <v>0.6846906072547312</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.185331827207228</v>
+        <v>-0.8431207673470674</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.45307018791447</v>
+        <v>2.658396823830567</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-6.331563569354985</v>
+        <v>-6.000786225947822</v>
       </c>
       <c r="E1888" t="n">
-        <v>0.6463408423479375</v>
+        <v>0.778651779710803</v>
       </c>
       <c r="F1888" t="n">
-        <v>-0.9880624214792301</v>
+        <v>-0.6458513616190693</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.586485241516141</v>
+        <v>2.791811877432238</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-6.132411462117886</v>
+        <v>-5.801634118710723</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.7129505515960939</v>
+        <v>0.8452614889589594</v>
       </c>
       <c r="F1889" t="n">
-        <v>-0.8227398955294167</v>
+        <v>-0.480528835669256</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.672627623439346</v>
+        <v>2.877954259355443</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-5.906566309398475</v>
+        <v>-5.575788965991312</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.8128676857200672</v>
+        <v>0.9451786230829327</v>
       </c>
       <c r="F1890" t="n">
-        <v>-0.7808132199422531</v>
+        <v>-0.4386021600820923</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.707362701827853</v>
+        <v>2.91268933774395</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-5.620291497075781</v>
+        <v>-5.289514153668618</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.9285167552052038</v>
+        <v>1.060827692568069</v>
       </c>
       <c r="F1891" t="n">
-        <v>-0.7808132199422531</v>
+        <v>-0.4386021600820923</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.708501846383912</v>
+        <v>2.913828482300008</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-5.393495670002448</v>
+        <v>-5.062718326595284</v>
       </c>
       <c r="E1892" t="n">
-        <v>1.021868860196645</v>
+        <v>1.15417979755951</v>
       </c>
       <c r="F1892" t="n">
-        <v>-0.7126992753207085</v>
+        <v>-0.3704882154605478</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.752003987318946</v>
+        <v>2.957330623235043</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76894809908157</v>
+        <v>3.768948099081565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-5.109586939073699</v>
+        <v>-4.778809595666536</v>
       </c>
       <c r="E1893" t="n">
-        <v>1.141166056806781</v>
+        <v>1.273476994169646</v>
       </c>
       <c r="F1893" t="n">
-        <v>-0.7126992753207085</v>
+        <v>-0.3704882154605478</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.757737691557583</v>
+        <v>2.963064327473679</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857435442533</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-4.862599688880747</v>
+        <v>-4.531822345473583</v>
       </c>
       <c r="E1894" t="n">
-        <v>1.230223694490097</v>
+        <v>1.362534631852962</v>
       </c>
       <c r="F1894" t="n">
-        <v>-0.4657120251277564</v>
+        <v>-0.1235009652675957</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.896192779279489</v>
+        <v>3.101519415195585</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-4.598762821676678</v>
+        <v>-4.267985478269514</v>
       </c>
       <c r="E1895" t="n">
-        <v>1.325874960058817</v>
+        <v>1.458185897421682</v>
       </c>
       <c r="F1895" t="n">
-        <v>-0.4657120251277564</v>
+        <v>-0.1235009652675957</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.886309297966581</v>
+        <v>3.091635933882678</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906231</v>
+        <v>3.766313503906226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-4.331521020808281</v>
+        <v>-4.000743677401117</v>
       </c>
       <c r="E1896" t="n">
-        <v>1.430937119906802</v>
+        <v>1.563248057269667</v>
       </c>
       <c r="F1896" t="n">
-        <v>-0.4657120251277564</v>
+        <v>-0.1235009652675957</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.884474737467208</v>
+        <v>3.089801373383304</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781951</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-4.055711857407797</v>
+        <v>-3.724934514000633</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.540960470293534</v>
+        <v>1.6732714076564</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.3766927168490229</v>
+        <v>-0.03448165698886219</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.937586007460987</v>
+        <v>3.142912643377083</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567247</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-3.786644269640818</v>
+        <v>-3.455866926233654</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.64925601154582</v>
+        <v>1.781566948908685</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.1076251290820436</v>
+        <v>0.2345859307781172</v>
       </c>
       <c r="G1898" t="n">
-        <v>3.099695066266668</v>
+        <v>3.305021702182764</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487776</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-3.522584331318021</v>
+        <v>-3.191806987910858</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.741619670713186</v>
+        <v>1.873930608076051</v>
       </c>
       <c r="F1899" t="n">
-        <v>0.1564348092407526</v>
+        <v>0.4986458691009134</v>
       </c>
       <c r="G1899" t="n">
-        <v>3.244870713098594</v>
+        <v>3.45019734901469</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83324917230973</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-2.815504707813183</v>
+        <v>-2.48472736440602</v>
       </c>
       <c r="E1900" t="n">
-        <v>2.02166448645482</v>
+        <v>2.153975423817686</v>
       </c>
       <c r="F1900" t="n">
-        <v>0.1564348092407526</v>
+        <v>0.4986458691009134</v>
       </c>
       <c r="G1900" t="n">
-        <v>3.242083679438293</v>
+        <v>3.447410315354389</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-2.565863677827232</v>
+        <v>-2.235086334420068</v>
       </c>
       <c r="E1901" t="n">
-        <v>2.121864522337042</v>
+        <v>2.254175459699908</v>
       </c>
       <c r="F1901" t="n">
-        <v>0.4060758392267043</v>
+        <v>0.7482868990868651</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.392211921317705</v>
+        <v>3.597538557233801</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096478</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-2.311321778486156</v>
+        <v>-1.980544435078993</v>
       </c>
       <c r="E1902" t="n">
-        <v>2.22304810329423</v>
+        <v>2.355359040657095</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.6606177385677798</v>
+        <v>1.002828798427941</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.544303882143107</v>
+        <v>3.749630518059204</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761811</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-2.077840556256558</v>
+        <v>-1.747063212849394</v>
       </c>
       <c r="E1903" t="n">
-        <v>2.324365021023922</v>
+        <v>2.456675958386787</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.8940989607973784</v>
+        <v>1.236310020657539</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.692317044318719</v>
+        <v>3.897643680234816</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255787</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-1.898132026112685</v>
+        <v>-1.567354682705522</v>
       </c>
       <c r="E1904" t="n">
-        <v>2.393356222768511</v>
+        <v>2.525667160131376</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.9512704649600745</v>
+        <v>1.293481524820235</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.723727736503378</v>
+        <v>3.929054372419474</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.439654578159369</v>
+        <v>3.439654578159365</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-1.712640208363002</v>
+        <v>-1.375849456140998</v>
       </c>
       <c r="E1905" t="n">
-        <v>2.462920436615411</v>
+        <v>2.597636737504213</v>
       </c>
       <c r="F1905" t="n">
-        <v>1.136762282709758</v>
+        <v>1.484986751384759</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.830390313900215</v>
+        <v>4.039324995105216</v>
       </c>
     </row>
   </sheetData>
